--- a/templates/登分表_九年级.xlsx
+++ b/templates/登分表_九年级.xlsx
@@ -701,7 +701,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">   只要某一列填了成绩，程序就把它当成本次考试的科目来统计。</t>
+          <t xml:space="preserve">   要加一门科目：在最后加一列，表头写科目名称（如 信息技术），下面填分数，程序会一起统计。</t>
         </is>
       </c>
     </row>
